--- a/参会人员名单 - 0506.xlsx
+++ b/参会人员名单 - 0506.xlsx
@@ -4,14 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9575"/>
+    <workbookView xWindow="240" yWindow="120" windowWidth="22188" windowHeight="9575" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames/>
+  <calcPr fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,37 +35,37 @@
     <t>参会人员名单</t>
   </si>
   <si>
-    <t>运维部</t>
+    <t>经营拓展部</t>
   </si>
   <si>
     <t>经理</t>
   </si>
   <si>
-    <t>程方</t>
+    <t>邹雪</t>
   </si>
   <si>
-    <t>研发部</t>
+    <t>技术研发中心</t>
   </si>
   <si>
-    <t>吴桀</t>
+    <t>陶海波</t>
   </si>
   <si>
-    <t>人力资源部</t>
+    <t>综合管理部</t>
   </si>
   <si>
-    <t>平湾</t>
+    <t>质量部</t>
   </si>
   <si>
-    <t>质量管理部</t>
-  </si>
-  <si>
-    <t>沈晓晖</t>
+    <t>彭炼</t>
   </si>
   <si>
     <t>管理者代表</t>
   </si>
   <si>
-    <t>茅建根</t>
+    <t>吴俊汐</t>
+  </si>
+  <si>
+    <t>刘汀</t>
   </si>
 </sst>
 </file>
@@ -77,40 +78,42 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -118,6 +121,7 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -126,6 +130,7 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -134,6 +139,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -142,6 +148,7 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -150,6 +157,7 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -158,6 +166,7 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -165,6 +174,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -173,6 +183,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -181,6 +192,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -189,6 +201,7 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -196,6 +209,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -204,6 +218,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -211,6 +226,7 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -218,6 +234,7 @@
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -225,6 +242,7 @@
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -232,18 +250,14 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -441,21 +455,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -471,7 +470,6 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -480,7 +478,6 @@
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -489,7 +486,6 @@
       <bottom style="medium">
         <color theme="4" tint="0.49998"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -504,7 +500,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -519,7 +514,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -534,7 +528,6 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -543,7 +536,6 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -554,238 +546,418 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="55">
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
+  <cellStyleXfs count="88">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
-      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
-      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
-      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="22" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="26" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="30" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0">
       <alignment vertical="center"/>
+      <protection/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="49" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="55">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="Normal" xfId="49"/>
-    <cellStyle name="Percent" xfId="50"/>
-    <cellStyle name="Currency" xfId="51"/>
-    <cellStyle name="Currency [0]" xfId="52"/>
-    <cellStyle name="Comma" xfId="53"/>
-    <cellStyle name="Comma [0]" xfId="54"/>
+  <cellStyles count="74">
+    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Percent" xfId="15"/>
+    <cellStyle name="Currency" xfId="16"/>
+    <cellStyle name="Currency [0]" xfId="17"/>
+    <cellStyle name="Comma" xfId="18"/>
+    <cellStyle name="Comma [0]" xfId="19"/>
+    <cellStyle name="Percent" xfId="20"/>
+    <cellStyle name="Currency" xfId="21"/>
+    <cellStyle name="Currency [0]" xfId="22"/>
+    <cellStyle name="Comma" xfId="23"/>
+    <cellStyle name="Comma [0]" xfId="24"/>
+    <cellStyle name="Percent" xfId="25"/>
+    <cellStyle name="Currency" xfId="26"/>
+    <cellStyle name="Currency [0]" xfId="27"/>
+    <cellStyle name="Comma" xfId="28"/>
+    <cellStyle name="Comma [0]" xfId="29"/>
+    <cellStyle name="Percent" xfId="30"/>
+    <cellStyle name="Currency" xfId="31"/>
+    <cellStyle name="Currency [0]" xfId="32"/>
+    <cellStyle name="Comma" xfId="33"/>
+    <cellStyle name="Comma [0]" xfId="34"/>
+    <cellStyle name="千位分隔" xfId="35"/>
+    <cellStyle name="货币" xfId="36"/>
+    <cellStyle name="百分比" xfId="37"/>
+    <cellStyle name="千位分隔[0]" xfId="38"/>
+    <cellStyle name="货币[0]" xfId="39"/>
+    <cellStyle name="超链接" xfId="40"/>
+    <cellStyle name="已访问的超链接" xfId="41"/>
+    <cellStyle name="注释" xfId="42"/>
+    <cellStyle name="警告文本" xfId="43"/>
+    <cellStyle name="标题" xfId="44"/>
+    <cellStyle name="解释性文本" xfId="45"/>
+    <cellStyle name="标题 1" xfId="46"/>
+    <cellStyle name="标题 2" xfId="47"/>
+    <cellStyle name="标题 3" xfId="48"/>
+    <cellStyle name="标题 4" xfId="49"/>
+    <cellStyle name="输入" xfId="50"/>
+    <cellStyle name="输出" xfId="51"/>
+    <cellStyle name="计算" xfId="52"/>
+    <cellStyle name="检查单元格" xfId="53"/>
+    <cellStyle name="链接单元格" xfId="54"/>
+    <cellStyle name="汇总" xfId="55"/>
+    <cellStyle name="好" xfId="56"/>
+    <cellStyle name="差" xfId="57"/>
+    <cellStyle name="适中" xfId="58"/>
+    <cellStyle name="强调文字颜色 1" xfId="59"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="60"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="61"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="62"/>
+    <cellStyle name="强调文字颜色 2" xfId="63"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="64"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="65"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="66"/>
+    <cellStyle name="强调文字颜色 3" xfId="67"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="68"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="69"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="70"/>
+    <cellStyle name="强调文字颜色 4" xfId="71"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="72"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="73"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="74"/>
+    <cellStyle name="强调文字颜色 5" xfId="75"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="76"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="77"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="78"/>
+    <cellStyle name="强调文字颜色 6" xfId="79"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="80"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="81"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="82"/>
+    <cellStyle name="Percent" xfId="83"/>
+    <cellStyle name="Currency" xfId="84"/>
+    <cellStyle name="Currency [0]" xfId="85"/>
+    <cellStyle name="Comma" xfId="86"/>
+    <cellStyle name="Comma [0]" xfId="87"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1043,21 +1215,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="14.1296296296296" customWidth="1"/>
+    <col min="1" max="1" width="14.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" ht="14.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" ht="14.4">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1065,13 +1236,13 @@
         <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" ht="14.4">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -1079,13 +1250,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" ht="14.4">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1093,36 +1264,36 @@
         <v>2</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="14.4">
+      <c r="A5" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="14.4">
+      <c r="A6" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1130,31 +1301,26 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>